--- a/report_cards/Report_Card_Akorede_Fathia.xlsx
+++ b/report_cards/Report_Card_Akorede_Fathia.xlsx
@@ -1591,7 +1591,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -1938,7 +1938,7 @@
       <c r="O36" s="36" t="n"/>
       <c r="P36" s="42" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Q36" s="35" t="n"/>
@@ -2053,7 +2053,7 @@
       <c r="O39" s="36" t="n"/>
       <c r="P39" s="42" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="Q39" s="35" t="n"/>

--- a/report_cards/Report_Card_Akorede_Fathia.xlsx
+++ b/report_cards/Report_Card_Akorede_Fathia.xlsx
@@ -1530,7 +1530,7 @@
       <c r="O28" s="36" t="n"/>
       <c r="P28" s="42" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="Q28" s="35" t="n"/>

--- a/report_cards/Report_Card_Akorede_Fathia.xlsx
+++ b/report_cards/Report_Card_Akorede_Fathia.xlsx
@@ -1870,16 +1870,32 @@
       <c r="D35" s="35" t="n"/>
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
-      <c r="G35" s="18" t="inlineStr"/>
-      <c r="H35" s="18" t="inlineStr"/>
+      <c r="G35" s="42" t="n">
+        <v>19</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>28</v>
+      </c>
       <c r="I35" s="36" t="n"/>
-      <c r="J35" s="18" t="inlineStr"/>
+      <c r="J35" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" s="36" t="n"/>
-      <c r="L35" s="18" t="inlineStr"/>
+      <c r="L35" s="18">
+        <f>SUM(G35, H35, J35)</f>
+        <v/>
+      </c>
       <c r="M35" s="36" t="n"/>
-      <c r="N35" s="18" t="inlineStr"/>
+      <c r="N35" s="18">
+        <f>IF(L35&gt;=75,"A1",IF(L35&gt;=70,"B2",IF(L35&gt;=65,"B3",IF(L35&gt;=60,"C4",IF(L35&gt;=55,"C5",IF(L35&gt;=50,"C6",IF(L35&gt;=45,"D7",IF(L35&gt;=40,"E8","F9"))))))))</f>
+        <v/>
+      </c>
       <c r="O35" s="36" t="n"/>
-      <c r="P35" s="18" t="inlineStr"/>
+      <c r="P35" s="42" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
       <c r="Q35" s="35" t="n"/>
       <c r="R35" s="36" t="n"/>
       <c r="T35" s="18" t="inlineStr">
@@ -2012,7 +2028,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>665</v>
+        <v>712</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2064,7 +2080,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>73.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2101,7 +2117,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>73.89%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2426,7 +2442,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>665</v>
+        <v>712</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2458,7 +2474,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>73.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2491,7 +2507,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>73.89%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>

--- a/report_cards/Report_Card_Akorede_Fathia.xlsx
+++ b/report_cards/Report_Card_Akorede_Fathia.xlsx
@@ -2247,7 +2247,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>

--- a/report_cards/Report_Card_Akorede_Fathia.xlsx
+++ b/report_cards/Report_Card_Akorede_Fathia.xlsx
@@ -1871,14 +1871,14 @@
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
       <c r="G35" s="42" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H35" s="42" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I35" s="36" t="n"/>
       <c r="J35" s="42" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K35" s="36" t="n"/>
       <c r="L35" s="18">
@@ -2247,7 +2247,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>
